--- a/cd3_automation_toolkit/example/CD3-CIS-ManagementServices-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-ManagementServices-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10512"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-master/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AC68A8-0A45-4749-9552-A8E5ABFEC231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BBC7D0-5A31-7F4E-8342-8765401678B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>

--- a/cd3_automation_toolkit/example/CD3-CIS-ManagementServices-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-ManagementServices-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9A8B70-5702-6A48-9F42-DA0101531AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464CEAA1-4FFC-A342-989F-54EC47EE0FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1920" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="1280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="1281">
   <si>
     <t>Region</t>
   </si>
@@ -4397,6 +4397,9 @@
       <t xml:space="preserve">Modified Notifications backend code
 </t>
     </r>
+  </si>
+  <si>
+    <t>Additional Data</t>
   </si>
 </sst>
 </file>
@@ -6989,7 +6992,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
@@ -7001,14 +7004,15 @@
     <col min="7" max="7" width="16.5" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" customWidth="1"/>
-    <col min="12" max="12" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.33203125" customWidth="1"/>
+    <col min="13" max="13" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="38" t="s">
         <v>1176</v>
       </c>
@@ -7022,9 +7026,10 @@
       <c r="I1" s="39"/>
       <c r="J1" s="39"/>
       <c r="K1" s="39"/>
-      <c r="L1" s="40"/>
-    </row>
-    <row r="2" spans="1:12" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="L1" s="39"/>
+      <c r="M1" s="40"/>
+    </row>
+    <row r="2" spans="1:13" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -7053,16 +7058,19 @@
         <v>17</v>
       </c>
       <c r="J2" s="6" t="s">
+        <v>1280</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -7090,15 +7098,16 @@
       <c r="I3" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="J3" s="7" t="b">
+      <c r="J3" s="7"/>
+      <c r="K3" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -7126,15 +7135,16 @@
       <c r="I4" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="J4" s="7" t="b">
+      <c r="J4" s="7"/>
+      <c r="K4" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M4" s="7"/>
+    </row>
+    <row r="5" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
@@ -7162,15 +7172,16 @@
       <c r="I5" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="J5" s="7" t="b">
+      <c r="J5" s="7"/>
+      <c r="K5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
@@ -7198,15 +7209,16 @@
       <c r="I6" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="J6" s="7" t="b">
+      <c r="J6" s="7"/>
+      <c r="K6" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="L6" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M6" s="7"/>
+    </row>
+    <row r="7" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
@@ -7234,15 +7246,16 @@
       <c r="I7" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="J7" s="7" t="b">
+      <c r="J7" s="7"/>
+      <c r="K7" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
@@ -7270,15 +7283,16 @@
       <c r="I8" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="J8" s="7" t="b">
+      <c r="J8" s="7"/>
+      <c r="K8" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M8" s="7"/>
+    </row>
+    <row r="9" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>7</v>
       </c>
@@ -7306,15 +7320,16 @@
       <c r="I9" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="J9" s="7" t="b">
+      <c r="J9" s="7"/>
+      <c r="K9" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M9" s="7"/>
+    </row>
+    <row r="10" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>7</v>
       </c>
@@ -7342,15 +7357,16 @@
       <c r="I10" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="J10" s="7" t="b">
+      <c r="J10" s="7"/>
+      <c r="K10" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="L10" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L10" s="7"/>
-    </row>
-    <row r="11" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M10" s="7"/>
+    </row>
+    <row r="11" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>7</v>
       </c>
@@ -7378,15 +7394,16 @@
       <c r="I11" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="J11" s="7" t="b">
+      <c r="J11" s="7"/>
+      <c r="K11" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="L11" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M11" s="7"/>
+    </row>
+    <row r="12" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>7</v>
       </c>
@@ -7414,15 +7431,16 @@
       <c r="I12" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="J12" s="7" t="b">
+      <c r="J12" s="7"/>
+      <c r="K12" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="L12" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L12" s="7"/>
-    </row>
-    <row r="13" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M12" s="7"/>
+    </row>
+    <row r="13" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
@@ -7450,15 +7468,16 @@
       <c r="I13" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="J13" s="7" t="b">
+      <c r="J13" s="7"/>
+      <c r="K13" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="L13" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L13" s="7"/>
-    </row>
-    <row r="14" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>7</v>
       </c>
@@ -7486,15 +7505,16 @@
       <c r="I14" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="J14" s="7" t="b">
+      <c r="J14" s="7"/>
+      <c r="K14" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="L14" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L14" s="7"/>
-    </row>
-    <row r="15" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>7</v>
       </c>
@@ -7522,15 +7542,16 @@
       <c r="I15" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="J15" s="7" t="b">
+      <c r="J15" s="7"/>
+      <c r="K15" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="L15" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>7</v>
       </c>
@@ -7558,15 +7579,16 @@
       <c r="I16" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="J16" s="7" t="b">
+      <c r="J16" s="7"/>
+      <c r="K16" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="L16" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L16" s="7"/>
-    </row>
-    <row r="17" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>7</v>
       </c>
@@ -7594,15 +7616,16 @@
       <c r="I17" s="7" t="s">
         <v>586</v>
       </c>
-      <c r="J17" s="7" t="b">
+      <c r="J17" s="7"/>
+      <c r="K17" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="L17" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -7630,15 +7653,16 @@
       <c r="I18" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="J18" s="7" t="b">
+      <c r="J18" s="7"/>
+      <c r="K18" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K18" s="7" t="s">
+      <c r="L18" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L18" s="7"/>
-    </row>
-    <row r="19" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>7</v>
       </c>
@@ -7666,15 +7690,16 @@
       <c r="I19" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="J19" s="7" t="b">
+      <c r="J19" s="7"/>
+      <c r="K19" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="L19" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L19" s="7"/>
-    </row>
-    <row r="20" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>7</v>
       </c>
@@ -7702,15 +7727,16 @@
       <c r="I20" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="J20" s="7" t="b">
+      <c r="J20" s="7"/>
+      <c r="K20" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L20" s="7"/>
-    </row>
-    <row r="21" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>7</v>
       </c>
@@ -7738,15 +7764,16 @@
       <c r="I21" s="7" t="s">
         <v>590</v>
       </c>
-      <c r="J21" s="7" t="b">
+      <c r="J21" s="7"/>
+      <c r="K21" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="L21" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="L21" s="7"/>
-    </row>
-    <row r="22" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>7</v>
       </c>
@@ -7774,15 +7801,16 @@
       <c r="I22" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="7" t="b">
+      <c r="J22" s="7"/>
+      <c r="K22" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="L22" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L22" s="7"/>
-    </row>
-    <row r="23" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>7</v>
       </c>
@@ -7810,15 +7838,16 @@
       <c r="I23" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J23" s="7" t="b">
+      <c r="J23" s="7"/>
+      <c r="K23" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="L23" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L23" s="7"/>
-    </row>
-    <row r="24" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>7</v>
       </c>
@@ -7846,15 +7875,16 @@
       <c r="I24" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J24" s="7" t="b">
+      <c r="J24" s="7"/>
+      <c r="K24" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="L24" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L24" s="7"/>
-    </row>
-    <row r="25" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M24" s="7"/>
+    </row>
+    <row r="25" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>7</v>
       </c>
@@ -7882,15 +7912,16 @@
       <c r="I25" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J25" s="7" t="b">
+      <c r="J25" s="7"/>
+      <c r="K25" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="L25" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L25" s="7"/>
-    </row>
-    <row r="26" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>7</v>
       </c>
@@ -7918,15 +7949,16 @@
       <c r="I26" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J26" s="7" t="b">
+      <c r="J26" s="7"/>
+      <c r="K26" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="L26" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L26" s="7"/>
-    </row>
-    <row r="27" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>7</v>
       </c>
@@ -7954,15 +7986,16 @@
       <c r="I27" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J27" s="7" t="b">
+      <c r="J27" s="7"/>
+      <c r="K27" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K27" s="7" t="s">
+      <c r="L27" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L27" s="7"/>
-    </row>
-    <row r="28" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>7</v>
       </c>
@@ -7990,15 +8023,16 @@
       <c r="I28" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J28" s="7" t="b">
+      <c r="J28" s="7"/>
+      <c r="K28" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K28" s="7" t="s">
+      <c r="L28" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L28" s="7"/>
-    </row>
-    <row r="29" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>7</v>
       </c>
@@ -8026,15 +8060,16 @@
       <c r="I29" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J29" s="7" t="b">
+      <c r="J29" s="7"/>
+      <c r="K29" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="L29" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L29" s="7"/>
-    </row>
-    <row r="30" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M29" s="7"/>
+    </row>
+    <row r="30" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>7</v>
       </c>
@@ -8062,15 +8097,16 @@
       <c r="I30" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J30" s="7" t="b">
+      <c r="J30" s="7"/>
+      <c r="K30" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K30" s="7" t="s">
+      <c r="L30" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L30" s="7"/>
-    </row>
-    <row r="31" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M30" s="7"/>
+    </row>
+    <row r="31" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>7</v>
       </c>
@@ -8098,15 +8134,16 @@
       <c r="I31" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J31" s="7" t="b">
+      <c r="J31" s="7"/>
+      <c r="K31" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K31" s="7" t="s">
+      <c r="L31" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L31" s="7"/>
-    </row>
-    <row r="32" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M31" s="7"/>
+    </row>
+    <row r="32" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>7</v>
       </c>
@@ -8134,15 +8171,16 @@
       <c r="I32" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J32" s="7" t="b">
+      <c r="J32" s="7"/>
+      <c r="K32" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K32" s="7" t="s">
+      <c r="L32" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L32" s="7"/>
-    </row>
-    <row r="33" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M32" s="7"/>
+    </row>
+    <row r="33" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>7</v>
       </c>
@@ -8170,15 +8208,16 @@
       <c r="I33" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J33" s="7" t="b">
+      <c r="J33" s="7"/>
+      <c r="K33" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K33" s="7" t="s">
+      <c r="L33" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L33" s="7"/>
-    </row>
-    <row r="34" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M33" s="7"/>
+    </row>
+    <row r="34" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>7</v>
       </c>
@@ -8206,15 +8245,16 @@
       <c r="I34" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J34" s="7" t="b">
+      <c r="J34" s="7"/>
+      <c r="K34" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K34" s="7" t="s">
+      <c r="L34" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L34" s="7"/>
-    </row>
-    <row r="35" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M34" s="7"/>
+    </row>
+    <row r="35" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>7</v>
       </c>
@@ -8242,15 +8282,16 @@
       <c r="I35" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J35" s="7" t="b">
+      <c r="J35" s="7"/>
+      <c r="K35" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K35" s="7" t="s">
+      <c r="L35" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L35" s="7"/>
-    </row>
-    <row r="36" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M35" s="7"/>
+    </row>
+    <row r="36" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>7</v>
       </c>
@@ -8278,15 +8319,16 @@
       <c r="I36" s="7" t="s">
         <v>1121</v>
       </c>
-      <c r="J36" s="7" t="b">
+      <c r="J36" s="7"/>
+      <c r="K36" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K36" s="7" t="s">
+      <c r="L36" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L36" s="7"/>
-    </row>
-    <row r="37" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M36" s="7"/>
+    </row>
+    <row r="37" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>7</v>
       </c>
@@ -8314,15 +8356,16 @@
       <c r="I37" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="J37" s="7" t="b">
+      <c r="J37" s="7"/>
+      <c r="K37" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K37" s="7" t="s">
+      <c r="L37" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L37" s="7"/>
-    </row>
-    <row r="38" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
         <v>7</v>
       </c>
@@ -8350,15 +8393,16 @@
       <c r="I38" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J38" s="7" t="b">
+      <c r="J38" s="7"/>
+      <c r="K38" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K38" s="7" t="s">
+      <c r="L38" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L38" s="7"/>
-    </row>
-    <row r="39" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M38" s="7"/>
+    </row>
+    <row r="39" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>7</v>
       </c>
@@ -8386,15 +8430,16 @@
       <c r="I39" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J39" s="7" t="b">
+      <c r="J39" s="7"/>
+      <c r="K39" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K39" s="7" t="s">
+      <c r="L39" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L39" s="7"/>
-    </row>
-    <row r="40" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M39" s="7"/>
+    </row>
+    <row r="40" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>7</v>
       </c>
@@ -8422,15 +8467,16 @@
       <c r="I40" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J40" s="7" t="b">
+      <c r="J40" s="7"/>
+      <c r="K40" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K40" s="7" t="s">
+      <c r="L40" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L40" s="7"/>
-    </row>
-    <row r="41" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M40" s="7"/>
+    </row>
+    <row r="41" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
         <v>7</v>
       </c>
@@ -8458,15 +8504,16 @@
       <c r="I41" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J41" s="7" t="b">
+      <c r="J41" s="7"/>
+      <c r="K41" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K41" s="7" t="s">
+      <c r="L41" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L41" s="7"/>
-    </row>
-    <row r="42" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M41" s="7"/>
+    </row>
+    <row r="42" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
         <v>7</v>
       </c>
@@ -8494,15 +8541,16 @@
       <c r="I42" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J42" s="7" t="b">
+      <c r="J42" s="7"/>
+      <c r="K42" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K42" s="7" t="s">
+      <c r="L42" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L42" s="7"/>
-    </row>
-    <row r="43" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M42" s="7"/>
+    </row>
+    <row r="43" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
         <v>7</v>
       </c>
@@ -8530,15 +8578,16 @@
       <c r="I43" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J43" s="7" t="b">
+      <c r="J43" s="7"/>
+      <c r="K43" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K43" s="7" t="s">
+      <c r="L43" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L43" s="7"/>
-    </row>
-    <row r="44" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M43" s="7"/>
+    </row>
+    <row r="44" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
         <v>7</v>
       </c>
@@ -8566,15 +8615,16 @@
       <c r="I44" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J44" s="7" t="b">
+      <c r="J44" s="7"/>
+      <c r="K44" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K44" s="7" t="s">
+      <c r="L44" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L44" s="7"/>
-    </row>
-    <row r="45" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M44" s="7"/>
+    </row>
+    <row r="45" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
         <v>7</v>
       </c>
@@ -8602,15 +8652,16 @@
       <c r="I45" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J45" s="7" t="b">
+      <c r="J45" s="7"/>
+      <c r="K45" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K45" s="7" t="s">
+      <c r="L45" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L45" s="7"/>
-    </row>
-    <row r="46" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M45" s="7"/>
+    </row>
+    <row r="46" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
         <v>7</v>
       </c>
@@ -8638,15 +8689,16 @@
       <c r="I46" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J46" s="7" t="b">
+      <c r="J46" s="7"/>
+      <c r="K46" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K46" s="7" t="s">
+      <c r="L46" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L46" s="7"/>
-    </row>
-    <row r="47" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M46" s="7"/>
+    </row>
+    <row r="47" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
         <v>7</v>
       </c>
@@ -8674,15 +8726,16 @@
       <c r="I47" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J47" s="7" t="b">
+      <c r="J47" s="7"/>
+      <c r="K47" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K47" s="7" t="s">
+      <c r="L47" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L47" s="7"/>
-    </row>
-    <row r="48" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M47" s="7"/>
+    </row>
+    <row r="48" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
         <v>7</v>
       </c>
@@ -8710,15 +8763,16 @@
       <c r="I48" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J48" s="7" t="b">
+      <c r="J48" s="7"/>
+      <c r="K48" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K48" s="7" t="s">
+      <c r="L48" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L48" s="7"/>
-    </row>
-    <row r="49" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M48" s="7"/>
+    </row>
+    <row r="49" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
         <v>7</v>
       </c>
@@ -8746,15 +8800,16 @@
       <c r="I49" s="7" t="s">
         <v>1253</v>
       </c>
-      <c r="J49" s="7" t="b">
+      <c r="J49" s="7"/>
+      <c r="K49" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K49" s="7" t="s">
+      <c r="L49" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L49" s="7"/>
-    </row>
-    <row r="50" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M49" s="7"/>
+    </row>
+    <row r="50" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
@@ -8782,15 +8837,16 @@
       <c r="I50" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J50" s="7" t="b">
+      <c r="J50" s="7"/>
+      <c r="K50" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K50" s="7" t="s">
+      <c r="L50" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L50" s="7"/>
-    </row>
-    <row r="51" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M50" s="7"/>
+    </row>
+    <row r="51" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
         <v>7</v>
       </c>
@@ -8818,15 +8874,16 @@
       <c r="I51" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J51" s="7" t="b">
+      <c r="J51" s="7"/>
+      <c r="K51" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K51" s="7" t="s">
+      <c r="L51" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L51" s="7"/>
-    </row>
-    <row r="52" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M51" s="7"/>
+    </row>
+    <row r="52" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
         <v>7</v>
       </c>
@@ -8854,15 +8911,16 @@
       <c r="I52" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J52" s="7" t="b">
+      <c r="J52" s="7"/>
+      <c r="K52" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K52" s="7" t="s">
+      <c r="L52" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L52" s="7"/>
-    </row>
-    <row r="53" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M52" s="7"/>
+    </row>
+    <row r="53" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
         <v>7</v>
       </c>
@@ -8890,15 +8948,16 @@
       <c r="I53" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J53" s="7" t="b">
+      <c r="J53" s="7"/>
+      <c r="K53" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K53" s="7" t="s">
+      <c r="L53" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L53" s="7"/>
-    </row>
-    <row r="54" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M53" s="7"/>
+    </row>
+    <row r="54" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
         <v>7</v>
       </c>
@@ -8926,15 +8985,16 @@
       <c r="I54" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J54" s="7" t="b">
+      <c r="J54" s="7"/>
+      <c r="K54" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K54" s="7" t="s">
+      <c r="L54" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L54" s="7"/>
-    </row>
-    <row r="55" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M54" s="7"/>
+    </row>
+    <row r="55" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
         <v>7</v>
       </c>
@@ -8962,15 +9022,16 @@
       <c r="I55" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J55" s="7" t="b">
+      <c r="J55" s="7"/>
+      <c r="K55" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K55" s="7" t="s">
+      <c r="L55" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L55" s="7"/>
-    </row>
-    <row r="56" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M55" s="7"/>
+    </row>
+    <row r="56" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
         <v>7</v>
       </c>
@@ -8998,15 +9059,16 @@
       <c r="I56" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J56" s="7" t="b">
+      <c r="J56" s="7"/>
+      <c r="K56" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K56" s="7" t="s">
+      <c r="L56" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L56" s="7"/>
-    </row>
-    <row r="57" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M56" s="7"/>
+    </row>
+    <row r="57" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
         <v>7</v>
       </c>
@@ -9034,15 +9096,16 @@
       <c r="I57" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J57" s="7" t="b">
+      <c r="J57" s="7"/>
+      <c r="K57" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K57" s="7" t="s">
+      <c r="L57" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L57" s="7"/>
-    </row>
-    <row r="58" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M57" s="7"/>
+    </row>
+    <row r="58" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
         <v>7</v>
       </c>
@@ -9070,15 +9133,16 @@
       <c r="I58" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J58" s="7" t="b">
+      <c r="J58" s="7"/>
+      <c r="K58" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K58" s="7" t="s">
+      <c r="L58" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L58" s="7"/>
-    </row>
-    <row r="59" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M58" s="7"/>
+    </row>
+    <row r="59" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
         <v>7</v>
       </c>
@@ -9106,15 +9170,16 @@
       <c r="I59" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J59" s="7" t="b">
+      <c r="J59" s="7"/>
+      <c r="K59" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K59" s="7" t="s">
+      <c r="L59" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L59" s="7"/>
-    </row>
-    <row r="60" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M59" s="7"/>
+    </row>
+    <row r="60" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
         <v>7</v>
       </c>
@@ -9142,15 +9207,16 @@
       <c r="I60" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J60" s="7" t="b">
+      <c r="J60" s="7"/>
+      <c r="K60" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K60" s="7" t="s">
+      <c r="L60" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="L60" s="7"/>
-    </row>
-    <row r="61" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M60" s="7"/>
+    </row>
+    <row r="61" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
         <v>7</v>
       </c>
@@ -9178,14 +9244,15 @@
       <c r="I61" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J61" s="7" t="b">
+      <c r="J61" s="7"/>
+      <c r="K61" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K61" s="7" t="s">
+      <c r="L61" s="7" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
         <v>7</v>
       </c>
@@ -9213,15 +9280,16 @@
       <c r="I62" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="J62" s="7" t="b">
+      <c r="J62" s="7"/>
+      <c r="K62" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K62" s="7" t="s">
+      <c r="L62" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="L62" s="7"/>
-    </row>
-    <row r="63" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M62" s="7"/>
+    </row>
+    <row r="63" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
         <v>7</v>
       </c>
@@ -9249,15 +9317,16 @@
       <c r="I63" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="J63" s="7" t="b">
+      <c r="J63" s="7"/>
+      <c r="K63" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K63" s="7" t="s">
+      <c r="L63" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="L63" s="7"/>
-    </row>
-    <row r="64" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M63" s="7"/>
+    </row>
+    <row r="64" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
         <v>7</v>
       </c>
@@ -9285,15 +9354,16 @@
       <c r="I64" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="J64" s="7" t="b">
+      <c r="J64" s="7"/>
+      <c r="K64" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K64" s="7" t="s">
+      <c r="L64" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="L64" s="7"/>
-    </row>
-    <row r="65" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M64" s="7"/>
+    </row>
+    <row r="65" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
         <v>7</v>
       </c>
@@ -9321,15 +9391,16 @@
       <c r="I65" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="J65" s="7" t="b">
+      <c r="J65" s="7"/>
+      <c r="K65" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K65" s="7" t="s">
+      <c r="L65" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="L65" s="7"/>
-    </row>
-    <row r="66" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M65" s="7"/>
+    </row>
+    <row r="66" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
         <v>7</v>
       </c>
@@ -9357,15 +9428,16 @@
       <c r="I66" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="J66" s="7" t="b">
+      <c r="J66" s="7"/>
+      <c r="K66" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K66" s="7" t="s">
+      <c r="L66" s="7" t="s">
         <v>1130</v>
       </c>
-      <c r="L66" s="7"/>
-    </row>
-    <row r="67" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M66" s="7"/>
+    </row>
+    <row r="67" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
         <v>7</v>
       </c>
@@ -9393,15 +9465,16 @@
       <c r="I67" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J67" s="7" t="b">
+      <c r="J67" s="7"/>
+      <c r="K67" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K67" s="7" t="s">
+      <c r="L67" s="7" t="s">
         <v>1129</v>
       </c>
-      <c r="L67" s="7"/>
-    </row>
-    <row r="68" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M67" s="7"/>
+    </row>
+    <row r="68" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
         <v>7</v>
       </c>
@@ -9429,15 +9502,16 @@
       <c r="I68" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J68" s="7" t="b">
+      <c r="J68" s="7"/>
+      <c r="K68" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K68" s="7" t="s">
+      <c r="L68" s="7" t="s">
         <v>1129</v>
       </c>
-      <c r="L68" s="7"/>
-    </row>
-    <row r="69" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M68" s="7"/>
+    </row>
+    <row r="69" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
         <v>7</v>
       </c>
@@ -9465,15 +9539,16 @@
       <c r="I69" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="J69" s="7" t="b">
+      <c r="J69" s="7"/>
+      <c r="K69" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K69" s="7" t="s">
+      <c r="L69" s="7" t="s">
         <v>1129</v>
       </c>
-      <c r="L69" s="7"/>
-    </row>
-    <row r="70" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="M69" s="7"/>
+    </row>
+    <row r="70" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
         <v>7</v>
       </c>
@@ -9501,15 +9576,16 @@
       <c r="I70" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="J70" s="7" t="b">
+      <c r="J70" s="7"/>
+      <c r="K70" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K70" s="7" t="s">
+      <c r="L70" s="7" t="s">
         <v>1129</v>
       </c>
-      <c r="L70" s="7"/>
-    </row>
-    <row r="71" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="M70" s="7"/>
+    </row>
+    <row r="71" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
         <v>7</v>
       </c>
@@ -9537,15 +9613,16 @@
       <c r="I71" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="J71" s="7" t="b">
+      <c r="J71" s="7"/>
+      <c r="K71" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K71" s="7" t="s">
+      <c r="L71" s="7" t="s">
         <v>1131</v>
       </c>
-      <c r="L71" s="7"/>
-    </row>
-    <row r="72" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="M71" s="7"/>
+    </row>
+    <row r="72" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
         <v>7</v>
       </c>
@@ -9573,15 +9650,16 @@
       <c r="I72" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="J72" s="7" t="b">
+      <c r="J72" s="7"/>
+      <c r="K72" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K72" s="7" t="s">
+      <c r="L72" s="7" t="s">
         <v>1131</v>
       </c>
-      <c r="L72" s="7"/>
-    </row>
-    <row r="73" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="M72" s="7"/>
+    </row>
+    <row r="73" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
         <v>7</v>
       </c>
@@ -9609,15 +9687,16 @@
       <c r="I73" s="7" t="s">
         <v>1149</v>
       </c>
-      <c r="J73" s="7" t="b">
+      <c r="J73" s="7"/>
+      <c r="K73" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K73" s="7" t="s">
+      <c r="L73" s="7" t="s">
         <v>1131</v>
       </c>
-      <c r="L73" s="7"/>
-    </row>
-    <row r="74" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="M73" s="7"/>
+    </row>
+    <row r="74" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
         <v>7</v>
       </c>
@@ -9645,15 +9724,16 @@
       <c r="I74" s="7" t="s">
         <v>1150</v>
       </c>
-      <c r="J74" s="7" t="b">
+      <c r="J74" s="7"/>
+      <c r="K74" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K74" s="7" t="s">
+      <c r="L74" s="7" t="s">
         <v>1131</v>
       </c>
-      <c r="L74" s="7"/>
-    </row>
-    <row r="75" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="M74" s="7"/>
+    </row>
+    <row r="75" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
         <v>7</v>
       </c>
@@ -9681,15 +9761,16 @@
       <c r="I75" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="J75" s="7" t="b">
+      <c r="J75" s="7"/>
+      <c r="K75" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K75" s="7" t="s">
+      <c r="L75" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="L75" s="8"/>
-    </row>
-    <row r="76" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="M75" s="8"/>
+    </row>
+    <row r="76" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
         <v>7</v>
       </c>
@@ -9717,15 +9798,16 @@
       <c r="I76" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="J76" s="7" t="b">
+      <c r="J76" s="7"/>
+      <c r="K76" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K76" s="7" t="s">
+      <c r="L76" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="L76" s="8"/>
-    </row>
-    <row r="77" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="M76" s="8"/>
+    </row>
+    <row r="77" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
         <v>7</v>
       </c>
@@ -9753,26 +9835,27 @@
       <c r="I77" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="J77" s="7" t="b">
+      <c r="J77" s="7"/>
+      <c r="K77" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="K77" s="7" t="s">
+      <c r="L77" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="I220:I1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="I220:J1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="I73:I219 I3:I70" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="I73:J219 I3:J70" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>INDIRECT(H3)</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" sqref="I71:I72" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="list" showInputMessage="1" sqref="I71:J72" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>INDIRECT(H71)</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="H3:H218" xr:uid="{00000000-0002-0000-0200-000002000000}">

--- a/cd3_automation_toolkit/example/CD3-CIS-ManagementServices-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-ManagementServices-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lasyavadavalli/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2317B500-F414-8B47-BBC2-125DC1AB2B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464CEAA1-4FFC-A342-989F-54EC47EE0FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6739,9 +6739,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential – Oracle Internal</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -6978,9 +6975,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential – Oracle Internal</oddFooter>
-  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -9870,9 +9864,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential – Oracle Internal</oddFooter>
-  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -10319,9 +10310,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential – Oracle Internal</oddFooter>
-  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -13282,9 +13270,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential – Oracle Internal</oddFooter>
-  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -13779,9 +13764,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential – Oracle Internal</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -15609,9 +15591,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential – Oracle Internal</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -17925,9 +17904,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential – Oracle Internal</oddFooter>
-  </headerFooter>
   <tableParts count="29">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>

--- a/cd3_automation_toolkit/example/CD3-CIS-ManagementServices-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-ManagementServices-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464CEAA1-4FFC-A342-989F-54EC47EE0FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7482395B-6684-7B4F-8B1F-46A648EBB2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4353,6 +4353,9 @@
     <t>Singapore-2</t>
   </si>
   <si>
+    <t>Additional Data</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -4383,8 +4386,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Release - v2025.2.0
-</t>
+      <t>Release - v2026.2.0</t>
     </r>
     <r>
       <rPr>
@@ -4394,12 +4396,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Modified Notifications backend code
+      <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>Additional Data</t>
   </si>
 </sst>
 </file>
@@ -6728,7 +6727,7 @@
     <row r="1" spans="1:1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="72.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
@@ -6739,6 +6738,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6975,6 +6978,10 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -7058,7 +7065,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
@@ -9864,6 +9871,10 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -10310,6 +10321,10 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -13270,6 +13285,10 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -13764,6 +13783,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -15591,6 +15614,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -17904,6 +17931,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
   <tableParts count="29">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -17936,4 +17967,10 @@
     <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{825c952f-1947-4719-99e7-7bc5a76060a8}" enabled="1" method="Standard" siteId="{4e2c6054-71cb-48f1-bd6c-3a9705aca71b}" contentBits="3" removed="0"/>
+</clbl:labelList>
 </file>